--- a/type/marketeur_data.xlsx
+++ b/type/marketeur_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
   <si>
     <t>Marketeur</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>Tradex</t>
+  </si>
+  <si>
+    <t>Elf</t>
   </si>
 </sst>
 </file>
@@ -383,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -416,6 +419,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/type/marketeur_data.xlsx
+++ b/type/marketeur_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
   <si>
     <t>Marketeur</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t>Elf</t>
+  </si>
+  <si>
+    <t>Green Oil</t>
   </si>
 </sst>
 </file>
@@ -386,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -430,6 +433,17 @@
         <v>4</v>
       </c>
     </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/type/marketeur_data.xlsx
+++ b/type/marketeur_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t>Marketeur</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>Green Oil</t>
+  </si>
+  <si>
+    <t>Neptune</t>
   </si>
 </sst>
 </file>
@@ -389,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -444,6 +447,17 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
